--- a/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\bin\Debug\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4E2162-D089-4FA7-9FF9-A566B805ACE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B85C3A-FCAA-470E-9F24-36AD06F40BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$J$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'PRICED (2)'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$23:$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$22:$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'PRICED (2)'!$23:$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>

--- a/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
@@ -8,19 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B85C3A-FCAA-470E-9F24-36AD06F40BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A0D789-2741-4A50-A146-A18E63BA4F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRICED" sheetId="1" r:id="rId1"/>
-    <sheet name="PRICED (2)" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$J$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'PRICED (2)'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$I$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$22:$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PRICED (2)'!$23:$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>QUOTATION</t>
   </si>
@@ -130,48 +127,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>60 DAYS</t>
-  </si>
-  <si>
-    <t>PENAGA/0010625/HESS</t>
-  </si>
-  <si>
-    <t>Prepared for:HESS EXPLORATION AND PRODUCTIONMALAYSIA B.V</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>DDP Tok Bali Supply Base</t>
-  </si>
-  <si>
-    <t>UNPRICED</t>
-  </si>
-  <si>
-    <t>QUOTED</t>
-  </si>
-  <si>
-    <t>HESS/2022/260</t>
-  </si>
-  <si>
-    <t>5  WEEKS</t>
-  </si>
-  <si>
-    <t>Model No :ZOK 27 CONCENTRATE</t>
-  </si>
-  <si>
-    <t>CLEANING FLUID with INHIBITOR</t>
-  </si>
-  <si>
-    <t>for Gas Turbine Compressor</t>
-  </si>
-  <si>
-    <t>Packaging :25 liter per pail</t>
-  </si>
-  <si>
-    <t>Manufacturer :ZOK International Group</t>
   </si>
   <si>
     <t>_date</t>
@@ -235,7 +190,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -291,13 +246,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="Cambria"/>
@@ -503,7 +451,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -528,7 +476,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -552,10 +499,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -565,16 +508,7 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -582,11 +516,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -597,13 +530,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -665,13 +598,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
@@ -739,13 +672,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -779,159 +712,6 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="704850" y="6800850"/>
-          <a:ext cx="952500" cy="962025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="penagaorb">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4381500" y="323850"/>
-          <a:ext cx="3000375" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="704850" y="6962775"/>
           <a:ext cx="952500" cy="962025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1254,650 +1034,314 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:J43"/>
+  <dimension ref="A3:I43"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C4" s="1" t="s">
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="1" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C8" s="1" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C9" s="1" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F11" s="4"/>
-      <c r="G11" s="5" t="s">
+    <row r="11" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E11" s="4"/>
+      <c r="F11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="6"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="44" t="s">
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="F12" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="47" t="s">
+      <c r="G12" s="39"/>
+      <c r="H12" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="48"/>
-    </row>
-    <row r="13" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="47" t="s">
+      <c r="I12" s="39"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="39"/>
+      <c r="H13" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="39"/>
+    </row>
+    <row r="15" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="48"/>
-    </row>
-    <row r="15" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B15" s="55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D20" s="1" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="12" t="s">
+      <c r="E20" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="B23" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="G23" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="I23" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
+      <c r="D24" s="15"/>
       <c r="E24" s="16"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="29"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="33"/>
-    </row>
-    <row r="27" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="40"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="40"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F29" s="39"/>
-      <c r="G29" s="41" t="s">
+      <c r="F24" s="16"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="22"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="25"/>
+    </row>
+    <row r="27" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="31"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="31"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="33"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E29" s="30"/>
+      <c r="F29" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="H29" s="42"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="36" t="s">
+      <c r="G29" s="33"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C34" s="36" t="s">
+    <row r="33" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B34" s="27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C35" s="36"/>
-    </row>
-    <row r="36" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C36" s="36" t="s">
+    <row r="35" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B35" s="27"/>
+    </row>
+    <row r="36" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B36" s="27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C37" s="36"/>
-    </row>
-    <row r="38" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C38" s="36"/>
-    </row>
-    <row r="39" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C39" s="36"/>
-    </row>
-    <row r="40" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C40" s="36"/>
-    </row>
-    <row r="41" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C41" s="36"/>
-    </row>
-    <row r="42" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C42" s="36" t="s">
+    <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B37" s="27"/>
+    </row>
+    <row r="38" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B38" s="27"/>
+    </row>
+    <row r="39" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B39" s="27"/>
+    </row>
+    <row r="40" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="27"/>
+    </row>
+    <row r="41" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="27"/>
+    </row>
+    <row r="42" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C43" s="36" t="s">
+    <row r="43" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="27" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.51181102362204722" right="0.47244094488188981" top="0.51181102362204722" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;RPage &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:J45"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F11" s="4"/>
-      <c r="G11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="47" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="48"/>
-    </row>
-    <row r="13" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F13" s="9">
-        <v>45170</v>
-      </c>
-      <c r="G13" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="48"/>
-    </row>
-    <row r="15" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="D20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19">
-        <v>1</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" s="24">
-        <v>16</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B26" s="19"/>
-      <c r="C26" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B27" s="19"/>
-      <c r="C27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B28" s="19"/>
-      <c r="C28" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="2:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19"/>
-      <c r="C29" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="2:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="33"/>
-    </row>
-    <row r="31" spans="2:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="34"/>
-      <c r="G31" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="42"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C36" s="36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C37" s="36"/>
-    </row>
-    <row r="38" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C38" s="36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C39" s="36"/>
-    </row>
-    <row r="40" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C40" s="36"/>
-    </row>
-    <row r="41" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C41" s="36"/>
-    </row>
-    <row r="42" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C42" s="36"/>
-    </row>
-    <row r="43" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C43" s="36"/>
-    </row>
-    <row r="44" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C44" s="36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C45" s="36" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C23:F23"/>
-  </mergeCells>
-  <pageMargins left="0.51181102362204722" right="0.47244094488188981" top="0.51181102362204722" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;RPage &amp;P</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A0D789-2741-4A50-A146-A18E63BA4F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80000009_{29A67964-E9BB-40CF-9DE0-5A26EBD047DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{902D2B79-FC85-4F11-86AF-3E75CBD52CE0}"/>
   </bookViews>
   <sheets>
     <sheet name="PRICED" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$I$43</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$22:$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$I$49</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$21:$22</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>QUOTATION</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Total Price (RM)</t>
   </si>
   <si>
-    <t>FAX: 03-87334865</t>
-  </si>
-  <si>
     <t>E-MAIL: penagaorb@gmail.com</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
     <t>Sales Executive</t>
   </si>
   <si>
+    <t>(1046887-P)</t>
+  </si>
+  <si>
     <t>BANDAR TEKNOLOGI KAJANG</t>
   </si>
   <si>
@@ -120,67 +120,73 @@
     <t>NO-14A, JALAN 1/6</t>
   </si>
   <si>
-    <t>Should you have any query, please do not hesitate to contact us at undersign person.</t>
-  </si>
-  <si>
-    <t>TEL: 03-82112306</t>
+    <t>TEL: 03-8211 2306</t>
+  </si>
+  <si>
+    <t>TERMS AND CONDITIONS :</t>
+  </si>
+  <si>
+    <t>1. PO cancellation fee is applied.</t>
+  </si>
+  <si>
+    <t>2. In the event of late payment after 60 days of dated invoice, 10% penalty upon PO value applied</t>
+  </si>
+  <si>
+    <t>_date</t>
+  </si>
+  <si>
+    <t>quote_code</t>
+  </si>
+  <si>
+    <t>rfq_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepared for: </t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>delivery_term</t>
+  </si>
+  <si>
+    <t>_validity</t>
+  </si>
+  <si>
+    <t>_num</t>
+  </si>
+  <si>
+    <t>_desc</t>
+  </si>
+  <si>
+    <t>delivery_time</t>
+  </si>
+  <si>
+    <t>_qty</t>
+  </si>
+  <si>
+    <t>unit_price</t>
+  </si>
+  <si>
+    <t>total_price</t>
+  </si>
+  <si>
+    <t>SUB TOTAL</t>
+  </si>
+  <si>
+    <t>sub_total</t>
+  </si>
+  <si>
+    <t>DISCOUNT</t>
+  </si>
+  <si>
+    <t>_discount</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>_date</t>
-  </si>
-  <si>
-    <t>quote_code</t>
-  </si>
-  <si>
-    <t>rfq_code</t>
-  </si>
-  <si>
-    <t>delivery_term</t>
-  </si>
-  <si>
-    <t>_validity</t>
-  </si>
-  <si>
-    <t>_num</t>
-  </si>
-  <si>
-    <t>_desc</t>
-  </si>
-  <si>
-    <t>delivery_time</t>
-  </si>
-  <si>
-    <t>_qty</t>
-  </si>
-  <si>
-    <t>unit_price</t>
-  </si>
-  <si>
-    <t>total_price</t>
-  </si>
-  <si>
-    <t>SUB TOTAL</t>
-  </si>
-  <si>
-    <t>sub_total</t>
-  </si>
-  <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
-    <t>_discount</t>
-  </si>
-  <si>
     <t>summary_total_price</t>
-  </si>
-  <si>
-    <t>Prepared for:</t>
-  </si>
-  <si>
-    <t>client_name</t>
   </si>
 </sst>
 </file>
@@ -188,9 +194,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -204,6 +214,13 @@
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -246,6 +263,19 @@
       <scheme val="major"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
       <sz val="14"/>
       <name val="Cambria"/>
@@ -253,7 +283,16 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Iskoola Pota"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Cambria"/>
       <family val="1"/>
       <scheme val="major"/>
@@ -273,7 +312,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -309,23 +348,10 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -335,10 +361,10 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -399,6 +425,19 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -425,161 +464,142 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{A18868C7-072C-4E8A-ADBD-C229F0B450EF}"/>
+    <cellStyle name="Normal 2 3" xfId="3" xr:uid="{B018C4B1-5EDE-40F8-ADFC-B054DC6230C0}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{7DB1CE62-59B7-4DD6-954A-116ABDECF58E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -598,32 +618,32 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>93258</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>80682</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>69776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1102" name="Picture 1" descr="penagaorb">
+        <xdr:cNvPr id="1154" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD7F716B-EF30-354D-0A6A-FF6E05BD9800}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -631,14 +651,12 @@
           </a:extLst>
         </a:blip>
         <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4886325" y="323850"/>
-          <a:ext cx="3000375" cy="952500"/>
+          <a:off x="477371" y="8044952"/>
+          <a:ext cx="894229" cy="729553"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -672,28 +690,28 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1103" name="Picture 1">
+        <xdr:cNvPr id="1153" name="Picture 1" descr="penagaorb">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E35056D7-B85A-9C93-C6FF-9482B2177B13}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -711,8 +729,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="704850" y="6800850"/>
-          <a:ext cx="952500" cy="962025"/>
+          <a:off x="4869180" y="335280"/>
+          <a:ext cx="3086100" cy="982980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1033,27 +1051,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:I43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E650388F-1D9A-4550-A538-2D37B2B47026}">
+  <dimension ref="A3:I50"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1072,7 +1092,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1080,268 +1100,329 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E11" s="4"/>
-      <c r="F11" s="5" t="s">
+    <row r="10" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E10" s="4"/>
+      <c r="F10" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="41"/>
+      <c r="H11" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="39"/>
-      <c r="H12" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="38" t="s">
+      <c r="E12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="38" t="s">
+      <c r="F12" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="15" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="41"/>
+    </row>
+    <row r="14" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29"/>
+    </row>
+    <row r="25" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E27" s="48"/>
+      <c r="F27" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="33"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+    </row>
+    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="33"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="33"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+    </row>
+    <row r="31" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A31" s="33"/>
+      <c r="B31" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+    </row>
+    <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="49"/>
+    </row>
+    <row r="33" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B34" s="49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B37" s="30"/>
+    </row>
+    <row r="38" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B38" s="30" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="25"/>
-    </row>
-    <row r="27" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="31"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="31"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="33"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E29" s="30"/>
-      <c r="F29" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G29" s="33"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="27" t="s">
+    <row r="39" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B39" s="30"/>
+    </row>
+    <row r="40" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="30" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="27"/>
-    </row>
-    <row r="36" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="27" t="s">
+    <row r="41" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="30"/>
+    </row>
+    <row r="42" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="30"/>
+    </row>
+    <row r="43" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="30"/>
+    </row>
+    <row r="44" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="30"/>
+    </row>
+    <row r="45" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="30"/>
+    </row>
+    <row r="46" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="27"/>
-    </row>
-    <row r="38" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="27"/>
-    </row>
-    <row r="39" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="27"/>
-    </row>
-    <row r="40" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="27"/>
-    </row>
-    <row r="41" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="27"/>
-    </row>
-    <row r="42" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="27" t="s">
+    <row r="47" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B47" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="27" t="s">
-        <v>23</v>
-      </c>
+    <row r="48" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B48" s="31"/>
+    </row>
+    <row r="49" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B49" s="31"/>
+    </row>
+    <row r="50" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B50" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="9">
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H11:I11"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.51181102362204722" right="0.47244094488188981" top="0.51181102362204722" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/PO TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80000009_{29A67964-E9BB-40CF-9DE0-5A26EBD047DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CC4EB9-60F7-42B8-9D1C-1383704259D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{902D2B79-FC85-4F11-86AF-3E75CBD52CE0}"/>
   </bookViews>
@@ -16,10 +16,10 @@
     <sheet name="PRICED" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$I$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$I$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$21:$22</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>QUOTATION</t>
   </si>
@@ -171,22 +171,10 @@
     <t>total_price</t>
   </si>
   <si>
-    <t>SUB TOTAL</t>
-  </si>
-  <si>
     <t>sub_total</t>
   </si>
   <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
-    <t>_discount</t>
-  </si>
-  <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>summary_total_price</t>
   </si>
 </sst>
 </file>
@@ -194,7 +182,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -467,12 +455,12 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -485,7 +473,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -497,7 +485,7 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -508,10 +496,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -529,7 +517,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -542,13 +530,26 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -573,26 +574,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -620,13 +601,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>93258</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>80682</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>69776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1052,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E650388F-1D9A-4550-A538-2D37B2B47026}">
-  <dimension ref="A3:I50"/>
+  <dimension ref="A3:I48"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="1" customWidth="1"/>
@@ -1110,36 +1091,36 @@
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="7"/>
       <c r="E11" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="41"/>
-      <c r="H11" s="40" t="s">
+      <c r="G11" s="46"/>
+      <c r="H11" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="41"/>
+      <c r="I11" s="46"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="40" t="s">
+      <c r="G12" s="46"/>
+      <c r="H12" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="41"/>
+      <c r="I12" s="46"/>
     </row>
     <row r="14" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -1191,12 +1172,12 @@
       <c r="A21" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
       <c r="F21" s="12" t="s">
         <v>13</v>
       </c>
@@ -1256,47 +1237,43 @@
       <c r="I24" s="29"/>
     </row>
     <row r="25" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="34" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="35"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E27" s="48"/>
-      <c r="F27" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G27" s="35"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="33"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+    </row>
+    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="33"/>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
@@ -1307,9 +1284,11 @@
       <c r="H28" s="33"/>
       <c r="I28" s="33"/>
     </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
+      <c r="B29" s="38" t="s">
+        <v>28</v>
+      </c>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
       <c r="E29" s="33"/>
@@ -1318,41 +1297,25 @@
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-    </row>
-    <row r="31" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
-      <c r="B31" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-    </row>
-    <row r="32" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="49"/>
-    </row>
-    <row r="33" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="38"/>
+    </row>
+    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B34" s="49" t="s">
+    <row r="32" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B32" s="38" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B35" s="30"/>
+    </row>
+    <row r="36" spans="2:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="B36" s="30" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.25">
@@ -1360,16 +1323,14 @@
     </row>
     <row r="38" spans="2:2" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="30"/>
     </row>
     <row r="40" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="30" t="s">
-        <v>20</v>
-      </c>
+      <c r="B40" s="30"/>
     </row>
     <row r="41" spans="2:2" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="30"/>
@@ -1381,34 +1342,26 @@
       <c r="B43" s="30"/>
     </row>
     <row r="44" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="30"/>
+      <c r="B44" s="30" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="45" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="30"/>
-    </row>
-    <row r="46" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="30" t="s">
+      <c r="B45" s="30" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="46" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B46" s="31"/>
+    </row>
+    <row r="47" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="B47" s="31"/>
     </row>
     <row r="48" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B48" s="31"/>
     </row>
-    <row r="49" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B49" s="31"/>
-    </row>
-    <row r="50" spans="2:2" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="B50" s="31"/>
-    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
+  <mergeCells count="7">
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B21:E21"/>
